--- a/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT_PV1_new30.xlsx
+++ b/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT_PV1_new30.xlsx
@@ -464,7 +464,9 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -482,7 +484,9 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -518,7 +522,9 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PV008448-PV008641, PV407014-PV407203, PV419497-PV419583</t>
+          <t>IN, PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -536,7 +542,9 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe
+```
+```</t>
         </is>
       </c>
     </row>
@@ -554,7 +562,9 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
+          <t>2022-2024
+```
+```</t>
         </is>
       </c>
     </row>
@@ -572,7 +582,9 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -590,7 +602,9 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -608,7 +622,9 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IN, PR, RT</t>
+          <t>Plasma, DBS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -626,7 +642,9 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -644,7 +662,9 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -662,7 +682,9 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>488
+```
+```</t>
         </is>
       </c>
     </row>
@@ -680,7 +702,9 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -698,7 +722,9 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -716,7 +742,8 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Tenofovir, lamivudine, dolutegravir
+```</t>
         </is>
       </c>
     </row>
@@ -734,7 +761,9 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -752,7 +781,9 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -770,7 +801,9 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -788,7 +821,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -806,7 +839,9 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -824,7 +859,9 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>England
+```
+```</t>
         </is>
       </c>
     </row>
@@ -842,7 +879,9 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>2017–2020
+```
+```</t>
         </is>
       </c>
     </row>
@@ -860,7 +899,9 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2017–2020</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -878,7 +919,9 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -896,7 +939,9 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -914,7 +959,9 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -932,7 +979,9 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -950,7 +999,9 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>54
+```
+```</t>
         </is>
       </c>
     </row>
@@ -968,7 +1019,9 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -986,7 +1039,9 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1059,8 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>TDF, FTC
+```</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1078,9 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TDF, FTC</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1098,9 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1118,9 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1138,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1156,9 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1176,9 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Switzerland
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1196,9 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>2015, 2022, 2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1216,9 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2015, 2022, 2023</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1236,9 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1256,9 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma, PBMC
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1276,9 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1296,9 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1316,9 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1336,9 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1356,9 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1376,8 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Zidovudine (AZT), Lamivudine (3TC), Abacavir (ABC), Tenofovir (TDF), Emtricitabine (FTC), Delavirdine (DLV), Efavirenz (EFV), Rilpivirine (RPV), Doravirine (DOR), Indinavir (IDV), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV), Raltegravir (RAL), Dolutegravir (DTG), Bictegravir (BIC), Fostemsavir (FTR)
+```</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1395,9 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Lamivudine (3TC), Abacavir (ABC), Tenofovir (TDF), Emtricitabine (FTC), Delavirdine (DLV), Efavirenz (EFV), Rilpivirine (RPV), Doravirine (DOR), Indinavir (IDV), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV), Raltegravir (RAL), Dolutegravir (DTG), Bictegravir (BIC), Fostemsavir (FTR)</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1415,9 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1435,9 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1455,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1473,9 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Pol
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1493,9 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>Argentina
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1513,9 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>2017-2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1533,9 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2017-2021</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1553,9 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1573,9 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1593,9 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1613,9 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1633,9 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1667
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1653,9 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1673,9 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1693,8 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1712,9 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1732,9 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1752,9 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1772,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1790,9 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1810,9 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>Kenya
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1830,9 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>2011-2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1850,9 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2011-2021</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1870,9 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1890,9 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1910,9 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1930,9 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1950,9 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>187
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1970,9 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1990,9 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1868,7 +2010,9 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>ATV/r, LPV/r
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1886,7 +2030,9 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ATV/r, LPV/r</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2050,9 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1922,7 +2070,9 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1940,7 +2090,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2108,9 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Env, Gag, Pol, PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2128,9 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>South Korea
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2148,9 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>2021–2024
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2168,9 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021–2024</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2188,9 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2208,9 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Env, Gag, Pol, PR, RT, IN</t>
+          <t>Plasma or serum
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2228,9 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2248,9 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Plasma or serum</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2268,9 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>487
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2288,9 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2308,9 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2328,8 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2347,9 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2367,9 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2387,9 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2425,9 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PV526713-PV526742</t>
+          <t>Pol
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2445,9 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Brazil
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2465,9 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>2021-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2485,9 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2505,9 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2525,9 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2545,9 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2565,9 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2585,9 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>30
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2605,9 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2625,9 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2645,8 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/Ritonavir, Efavirenz (EFV)
+```</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2664,9 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/Ritonavir, Efavirenz (EFV)</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2684,9 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2704,9 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2724,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2742,9 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2762,9 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Ghana
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2782,9 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2802,9 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2822,9 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2842,9 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2862,9 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2882,9 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2902,9 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>20
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2922,9 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2942,9 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2962,8 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>K103N, M184I/V
+```</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2981,9 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>K103N, M184I/V</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2768,7 +3001,9 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2786,7 +3021,9 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2804,7 +3041,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2822,7 +3059,9 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2840,7 +3079,9 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>Uganda
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3099,9 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2021-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2876,7 +3119,9 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>Sanger sequencing, NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2894,7 +3139,9 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2912,7 +3159,9 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma, DBS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2930,7 +3179,9 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3199,9 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2966,7 +3219,9 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>295
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2984,7 +3239,9 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3259,9 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3279,8 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3298,9 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3318,9 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3338,9 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3358,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3376,9 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3396,9 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3416,9 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3436,9 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3456,9 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3476,9 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Whole blood
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3496,9 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3516,9 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3536,9 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2028
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3556,9 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3576,9 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3596,8 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>TDF/TAF, EFV, ETR, RPV, NVP, DTG, BIC, LPV/r, ATV
+```</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3615,9 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TDF/TAF, EFV, ETR, RPV, NVP, DTG, BIC, LPV/r, ATV</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3635,9 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3655,9 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3675,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3693,9 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3713,9 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>Malawi
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3733,9 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>2022–2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3753,9 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3773,9 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3793,9 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3813,9 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3833,9 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3853,9 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>213
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3873,9 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3893,9 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTIs
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3913,8 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>INSTIs</t>
+          <t>Dolutegravir
+```</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3932,9 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Dolutegravir</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3952,9 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3972,9 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3992,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3686,7 +4010,9 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3704,7 +4030,9 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>10
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3722,7 +4050,9 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3740,7 +4070,9 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3758,7 +4090,9 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3776,7 +4110,9 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3794,7 +4130,9 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3812,7 +4150,9 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3830,7 +4170,9 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>208
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3848,7 +4190,9 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3866,7 +4210,9 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3884,7 +4230,8 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>TDF, FTC, B/F/TAF, DTG
+```</t>
         </is>
       </c>
     </row>
@@ -3902,7 +4249,9 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>TDF, FTC, B/F/TAF, DTG</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3920,7 +4269,9 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3938,7 +4289,9 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4309,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3974,7 +4327,9 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN, Pol
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4347,9 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>Tanzania
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4367,9 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4387,9 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4407,9 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4427,9 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4447,9 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4467,9 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4487,9 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>9685
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4507,9 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4527,9 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4547,8 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4566,9 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4586,9 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4606,9 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4644,9 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PX133190-PX134237</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4664,9 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>China
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4684,9 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>2019-2022
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4704,9 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4724,9 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4744,9 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4764,9 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4784,9 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4804,9 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1260
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4824,9 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4844,9 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4864,8 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4883,9 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4903,9 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4923,9 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4961,9 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4981,9 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4586,7 +5001,9 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4604,7 +5021,9 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4622,7 +5041,9 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4640,7 +5061,9 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4658,7 +5081,9 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4676,7 +5101,9 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4694,7 +5121,9 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>0
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4712,7 +5141,9 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4730,7 +5161,9 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4748,7 +5181,8 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```</t>
         </is>
       </c>
     </row>
@@ -4766,7 +5200,9 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4784,7 +5220,9 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5240,9 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4820,7 +5260,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4838,7 +5278,9 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4856,7 +5298,9 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4874,7 +5318,9 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4892,7 +5338,9 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4910,7 +5358,9 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5378,9 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4946,7 +5398,9 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4964,7 +5418,9 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4982,7 +5438,9 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>24
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5458,9 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5478,9 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5498,8 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5517,9 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5537,9 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5557,9 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5577,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5595,9 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5615,9 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5635,9 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1997-2019
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5655,9 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>1997-2019</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5675,9 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5695,9 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Whole blood
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5715,9 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5735,9 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5755,9 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>223
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5775,9 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5795,9 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI, NRTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5815,8 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir alafenamide
+```</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5834,9 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Bictegravir, Emtricitabine, Tenofovir alafenamide</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5854,9 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5874,9 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5894,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5912,9 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Env, NC
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5932,9 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>United Kingdom
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5952,9 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>2015–2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5972,9 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2015–2021</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5992,9 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5504,7 +6012,9 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Env, NC</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5522,7 +6032,9 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5540,7 +6052,9 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5558,7 +6072,9 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1182
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5576,7 +6092,9 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5594,7 +6112,9 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5612,7 +6132,8 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -5630,7 +6151,9 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5648,7 +6171,9 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5666,7 +6191,9 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5702,7 +6229,9 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5720,7 +6249,9 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5738,7 +6269,9 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5756,7 +6289,9 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5774,7 +6309,9 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5792,7 +6329,9 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5810,7 +6349,9 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5828,7 +6369,9 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5846,7 +6389,9 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>249
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5864,7 +6409,9 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5882,7 +6429,9 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5900,7 +6449,8 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -5918,7 +6468,9 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5936,7 +6488,9 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5954,7 +6508,9 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5972,7 +6528,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5990,7 +6546,9 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6566,9 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Mozambique
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6586,9 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>2023–2024
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6606,9 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2023–2024</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6626,9 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6646,9 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6666,9 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6686,9 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6706,9 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>28
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6726,9 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6746,9 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6766,8 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6785,9 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6805,9 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6825,9 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6863,9 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>PQ893197, PQ893192, OQ985810, OR259747, PQ893191</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6883,9 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>Cameroon
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6903,9 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>2022-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6923,9 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6943,9 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6963,9 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6983,9 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6404,7 +7003,9 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6422,7 +7023,9 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>203
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6440,7 +7043,9 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6458,7 +7063,9 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6476,7 +7083,8 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>ABC, 3TC, EFV, NVP, AZT, DTG, ATV, LPV, TDF
+```</t>
         </is>
       </c>
     </row>
@@ -6494,7 +7102,9 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>ABC, 3TC, EFV, NVP, AZT, DTG, ATV, LPV, TDF</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6512,7 +7122,9 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6530,7 +7142,9 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6548,7 +7162,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6566,7 +7180,9 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>CA
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6584,7 +7200,9 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>USA, Dominican Republic
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6602,7 +7220,9 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>2019–2020
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6620,7 +7240,9 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2019–2020</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6638,7 +7260,9 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6656,7 +7280,9 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6674,7 +7300,9 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6692,7 +7320,9 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6710,7 +7340,9 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>182
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6728,7 +7360,9 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6746,7 +7380,9 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6764,7 +7400,8 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Emtricitabine (FTC); Tenofovir alafenamide (TAF); Bictegravir (BIC); Lenacapavir (LEN)
+```</t>
         </is>
       </c>
     </row>
@@ -6782,7 +7419,9 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Emtricitabine (FTC); Tenofovir alafenamide (TAF); Bictegravir (BIC); Lenacapavir (LEN)</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6800,7 +7439,9 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7459,9 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6836,7 +7479,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6854,7 +7497,9 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN, Pol, CA, Env
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6872,7 +7517,9 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>Uganda
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6890,7 +7537,9 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2018–2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6908,7 +7557,9 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2018–2023</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6926,7 +7577,9 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6944,7 +7597,9 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol, CA, Env</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6962,7 +7617,9 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6980,7 +7637,9 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6998,7 +7657,9 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>235
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7677,9 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7697,9 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7717,8 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>ABC, AZT, TDF, FTC, LPV, RTV, d4T, DRV, RAL
+```</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7736,9 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>ABC, AZT, TDF, FTC, LPV, RTV, d4T, DRV, RAL</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7756,9 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7776,9 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7814,9 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>PV187006</t>
+          <t>Pol
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7834,9 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>China
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7854,9 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7874,9 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7894,9 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7914,9 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Plasma, whole blood
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7934,9 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7954,9 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Plasma, whole blood</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7974,9 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7994,9 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7322,7 +8014,9 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7340,7 +8034,8 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -7358,7 +8053,9 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7376,7 +8073,9 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7394,7 +8093,9 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7412,7 +8113,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7430,7 +8131,9 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7448,7 +8151,9 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7466,7 +8171,9 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7484,7 +8191,9 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7502,7 +8211,9 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7520,7 +8231,9 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7538,7 +8251,9 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7556,7 +8271,9 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7574,7 +8291,9 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7592,7 +8311,9 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7610,7 +8331,9 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7628,7 +8351,8 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -7646,7 +8370,9 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7664,7 +8390,9 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7682,7 +8410,9 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7700,7 +8430,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7718,7 +8448,9 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>PQ735970-PQ735985</t>
+          <t>Pol
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7736,7 +8468,9 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>China, United States
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7754,7 +8488,9 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>1978–2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7772,7 +8508,9 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1978–2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7790,7 +8528,9 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7808,7 +8548,9 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7826,7 +8568,9 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7844,7 +8588,9 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7862,7 +8608,9 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>0
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7880,7 +8628,9 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7898,7 +8648,9 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7916,7 +8668,8 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```</t>
         </is>
       </c>
     </row>
@@ -7934,7 +8687,9 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7952,7 +8707,9 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7970,7 +8727,9 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8765,9 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>PP280627 to PP280757</t>
+          <t>RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8785,9 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>Senegal
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8805,9 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>2017-2018
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8825,9 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2017-2018</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8845,9 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8865,9 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Plasma, DBS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8885,9 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8905,9 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8925,9 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>237
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8945,9 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8965,9 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8985,8 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -8222,7 +9004,9 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8240,7 +9024,9 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8258,7 +9044,9 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8276,7 +9064,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8294,7 +9082,9 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8312,7 +9102,9 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>Uganda
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8330,7 +9122,9 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8348,7 +9142,9 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8366,7 +9162,9 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8384,7 +9182,9 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8402,7 +9202,9 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8420,7 +9222,9 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8438,7 +9242,9 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>333
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8456,7 +9262,9 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8474,7 +9282,9 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8492,7 +9302,8 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>DTG, LPV/r, EFV, NVP, ABC, AZT, TDF, 3TC
+```</t>
         </is>
       </c>
     </row>
@@ -8510,7 +9321,9 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>DTG, LPV/r, EFV, NVP, ABC, AZT, TDF, 3TC</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8528,7 +9341,9 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8546,7 +9361,9 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8564,7 +9381,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8582,7 +9399,9 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>CA, PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8600,7 +9419,9 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8618,7 +9439,9 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8636,7 +9459,9 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8654,7 +9479,9 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8672,7 +9499,9 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>CA, PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8690,7 +9519,9 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8708,7 +9539,9 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8726,7 +9559,9 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>52
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8744,7 +9579,9 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8762,7 +9599,9 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8780,7 +9619,8 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -8798,7 +9638,9 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8816,7 +9658,9 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8834,7 +9678,9 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8870,7 +9716,9 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8888,7 +9736,9 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Kenya, Uganda, Tanzania, Ethiopia
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8906,7 +9756,9 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Kenya, Uganda, Tanzania, Ethiopia</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8924,7 +9776,9 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8942,7 +9796,9 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8960,7 +9816,9 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8978,7 +9836,9 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8996,7 +9856,9 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9876,9 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9896,9 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9916,9 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9936,8 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9955,9 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>

--- a/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT_PV1_new30.xlsx
+++ b/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT_PV1_new30.xlsx
@@ -464,9 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -484,9 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -522,9 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IN, PR, RT
-```
-```</t>
+          <t>IN, PR, RT</t>
         </is>
       </c>
     </row>
@@ -542,9 +536,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe
-```
-```</t>
+          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
         </is>
       </c>
     </row>
@@ -562,9 +554,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2022-2024
-```
-```</t>
+          <t>2022-2024</t>
         </is>
       </c>
     </row>
@@ -582,9 +572,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -602,9 +590,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -622,9 +608,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Plasma, DBS
-```
-```</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
     </row>
@@ -642,9 +626,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -662,9 +644,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -682,9 +662,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>488
-```
-```</t>
+          <t>488</t>
         </is>
       </c>
     </row>
@@ -702,9 +680,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -722,9 +698,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
     </row>
@@ -742,8 +716,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir
-```</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
     </row>
@@ -761,9 +734,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -781,9 +752,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -801,9 +770,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -839,9 +806,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -859,9 +824,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>England
-```
-```</t>
+          <t>England</t>
         </is>
       </c>
     </row>
@@ -879,9 +842,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2017–2020
-```
-```</t>
+          <t>2017–2020</t>
         </is>
       </c>
     </row>
@@ -899,9 +860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -919,9 +878,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -939,9 +896,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -959,9 +914,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -979,9 +932,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -999,9 +950,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54
-```
-```</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -1019,9 +968,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1039,9 +986,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NRTI
-```
-```</t>
+          <t>NRTI</t>
         </is>
       </c>
     </row>
@@ -1059,8 +1004,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TDF, FTC
-```</t>
+          <t>TDF, FTC</t>
         </is>
       </c>
     </row>
@@ -1078,9 +1022,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1098,9 +1040,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1118,9 +1058,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1156,9 +1094,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -1176,9 +1112,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Switzerland
-```
-```</t>
+          <t>Switzerland</t>
         </is>
       </c>
     </row>
@@ -1196,9 +1130,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2015, 2022, 2023
-```
-```</t>
+          <t>2015, 2022, 2023</t>
         </is>
       </c>
     </row>
@@ -1216,9 +1148,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -1236,9 +1166,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -1256,9 +1184,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Plasma, PBMC
-```
-```</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
     </row>
@@ -1276,9 +1202,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1296,9 +1220,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1316,9 +1238,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1
-```
-```</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1336,9 +1256,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1356,9 +1274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -1376,8 +1292,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Lamivudine (3TC), Abacavir (ABC), Tenofovir (TDF), Emtricitabine (FTC), Delavirdine (DLV), Efavirenz (EFV), Rilpivirine (RPV), Doravirine (DOR), Indinavir (IDV), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV), Raltegravir (RAL), Dolutegravir (DTG), Bictegravir (BIC), Fostemsavir (FTR)
-```</t>
+          <t>Zidovudine (AZT), Lamivudine (3TC), Abacavir (ABC), Tenofovir (TDF), Emtricitabine (FTC), Delavirdine (DLV), Efavirenz (EFV), Rilpivirine (RPV), Doravirine (DOR), Indinavir (IDV), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV), Raltegravir (RAL), Dolutegravir (DTG), Bictegravir (BIC), Fostemsavir (FTR)</t>
         </is>
       </c>
     </row>
@@ -1395,9 +1310,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1415,9 +1328,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1435,9 +1346,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1473,9 +1382,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pol
-```
-```</t>
+          <t>Pol</t>
         </is>
       </c>
     </row>
@@ -1493,9 +1400,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Argentina
-```
-```</t>
+          <t>Argentina</t>
         </is>
       </c>
     </row>
@@ -1513,9 +1418,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2017-2021
-```
-```</t>
+          <t>2017-2021</t>
         </is>
       </c>
     </row>
@@ -1533,9 +1436,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -1553,9 +1454,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1573,9 +1472,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -1593,9 +1490,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1613,9 +1508,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1633,9 +1526,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1667
-```
-```</t>
+          <t>1667</t>
         </is>
       </c>
     </row>
@@ -1653,9 +1544,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1673,9 +1562,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1693,8 +1580,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1712,9 +1598,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1732,9 +1616,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1752,9 +1634,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1790,9 +1670,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -1810,9 +1688,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kenya
-```
-```</t>
+          <t>Kenya</t>
         </is>
       </c>
     </row>
@@ -1830,9 +1706,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2011-2021
-```
-```</t>
+          <t>2011-2021</t>
         </is>
       </c>
     </row>
@@ -1850,9 +1724,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -1870,9 +1742,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,9 +1760,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -1910,9 +1778,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1930,9 +1796,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1950,9 +1814,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>187
-```
-```</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -1970,9 +1832,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1990,9 +1850,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI
-```
-```</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
     </row>
@@ -2010,9 +1868,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ATV/r, LPV/r
-```
-```</t>
+          <t>ATV/r, LPV/r</t>
         </is>
       </c>
     </row>
@@ -2030,9 +1886,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2050,9 +1904,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2070,9 +1922,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2108,9 +1958,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Env, Gag, Pol, PR, RT, IN
-```
-```</t>
+          <t>Env, Gag, Pol, PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -2128,9 +1976,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>South Korea
-```
-```</t>
+          <t>South Korea</t>
         </is>
       </c>
     </row>
@@ -2148,9 +1994,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021–2024
-```
-```</t>
+          <t>2021–2024</t>
         </is>
       </c>
     </row>
@@ -2168,9 +2012,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -2188,9 +2030,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2208,9 +2048,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Plasma or serum
-```
-```</t>
+          <t>Plasma or serum</t>
         </is>
       </c>
     </row>
@@ -2228,9 +2066,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2248,9 +2084,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2268,9 +2102,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>487
-```
-```</t>
+          <t>487</t>
         </is>
       </c>
     </row>
@@ -2288,9 +2120,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2308,9 +2138,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2328,8 +2156,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2347,9 +2174,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2367,9 +2192,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2387,9 +2210,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2425,9 +2246,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Pol
-```
-```</t>
+          <t>Pol</t>
         </is>
       </c>
     </row>
@@ -2445,9 +2264,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Brazil
-```
-```</t>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -2465,9 +2282,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2021-2023
-```
-```</t>
+          <t>2021-2023</t>
         </is>
       </c>
     </row>
@@ -2485,9 +2300,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -2505,9 +2318,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2525,9 +2336,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -2545,9 +2354,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2565,9 +2372,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2585,9 +2390,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>30
-```
-```</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2605,9 +2408,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2625,9 +2426,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI
-```
-```</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
     </row>
@@ -2645,8 +2444,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/Ritonavir, Efavirenz (EFV)
-```</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/Ritonavir, Efavirenz (EFV)</t>
         </is>
       </c>
     </row>
@@ -2664,9 +2462,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2684,9 +2480,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2704,9 +2498,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2742,9 +2534,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -2762,9 +2552,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ghana
-```
-```</t>
+          <t>Ghana</t>
         </is>
       </c>
     </row>
@@ -2782,9 +2570,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -2802,9 +2588,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -2822,9 +2606,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -2842,9 +2624,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -2862,9 +2642,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2882,9 +2660,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2902,9 +2678,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20
-```
-```</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2922,9 +2696,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2942,9 +2714,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI
-```
-```</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
     </row>
@@ -2962,8 +2732,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>K103N, M184I/V
-```</t>
+          <t>K103N, M184I/V</t>
         </is>
       </c>
     </row>
@@ -2981,9 +2750,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3001,9 +2768,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3021,9 +2786,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3059,9 +2822,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -3079,9 +2840,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Uganda
-```
-```</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -3099,9 +2858,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2021-2023
-```
-```</t>
+          <t>2021-2023</t>
         </is>
       </c>
     </row>
@@ -3119,9 +2876,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS
-```
-```</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
     </row>
@@ -3139,9 +2894,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3159,9 +2912,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Plasma, DBS
-```
-```</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
     </row>
@@ -3179,9 +2930,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3199,9 +2948,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3219,9 +2966,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>295
-```
-```</t>
+          <t>295</t>
         </is>
       </c>
     </row>
@@ -3239,9 +2984,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3259,9 +3002,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -3279,8 +3020,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3298,9 +3038,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3318,9 +3056,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3338,9 +3074,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3376,9 +3110,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -3396,9 +3128,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3416,9 +3146,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3436,9 +3164,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -3456,9 +3182,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3476,9 +3200,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Whole blood
-```
-```</t>
+          <t>Whole blood</t>
         </is>
       </c>
     </row>
@@ -3496,9 +3218,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3516,9 +3236,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3536,9 +3254,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2028
-```
-```</t>
+          <t>2028</t>
         </is>
       </c>
     </row>
@@ -3556,9 +3272,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3576,9 +3290,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -3596,8 +3308,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TDF/TAF, EFV, ETR, RPV, NVP, DTG, BIC, LPV/r, ATV
-```</t>
+          <t>TDF/TAF, EFV, ETR, RPV, NVP, DTG, BIC, LPV/r, ATV</t>
         </is>
       </c>
     </row>
@@ -3615,9 +3326,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3635,9 +3344,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3655,9 +3362,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3693,9 +3398,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -3713,9 +3416,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Malawi
-```
-```</t>
+          <t>Malawi</t>
         </is>
       </c>
     </row>
@@ -3733,9 +3434,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2022–2023
-```
-```</t>
+          <t>2022–2023</t>
         </is>
       </c>
     </row>
@@ -3753,9 +3452,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -3773,9 +3470,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3793,9 +3488,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -3813,9 +3506,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3833,9 +3524,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3853,9 +3542,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>213
-```
-```</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -3873,9 +3560,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3893,9 +3578,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>INSTIs
-```
-```</t>
+          <t>INSTIs</t>
         </is>
       </c>
     </row>
@@ -3913,8 +3596,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Dolutegravir
-```</t>
+          <t>Dolutegravir</t>
         </is>
       </c>
     </row>
@@ -3932,9 +3614,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3952,9 +3632,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3972,9 +3650,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4010,9 +3686,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -4030,9 +3704,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>10
-```
-```</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4050,9 +3722,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4070,9 +3740,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4090,9 +3758,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4110,9 +3776,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -4130,9 +3794,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4150,9 +3812,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4170,9 +3830,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>208
-```
-```</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -4190,9 +3848,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4210,9 +3866,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NRTI
-```
-```</t>
+          <t>NRTI</t>
         </is>
       </c>
     </row>
@@ -4230,8 +3884,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TDF, FTC, B/F/TAF, DTG
-```</t>
+          <t>TDF, FTC, B/F/TAF, DTG</t>
         </is>
       </c>
     </row>
@@ -4249,9 +3902,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4269,9 +3920,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4289,9 +3938,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4327,9 +3974,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol
-```
-```</t>
+          <t>PR, RT, IN, Pol</t>
         </is>
       </c>
     </row>
@@ -4347,9 +3992,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Tanzania
-```
-```</t>
+          <t>Tanzania</t>
         </is>
       </c>
     </row>
@@ -4367,9 +4010,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4387,9 +4028,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4407,9 +4046,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4427,9 +4064,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -4447,9 +4082,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4467,9 +4100,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4487,9 +4118,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>9685
-```
-```</t>
+          <t>9685</t>
         </is>
       </c>
     </row>
@@ -4507,9 +4136,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4527,9 +4154,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -4547,8 +4172,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4566,9 +4190,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4586,9 +4208,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4606,9 +4226,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4644,9 +4262,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -4664,9 +4280,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>China
-```
-```</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -4684,9 +4298,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2019-2022
-```
-```</t>
+          <t>2019-2022</t>
         </is>
       </c>
     </row>
@@ -4704,9 +4316,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -4724,9 +4334,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4744,9 +4352,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -4764,9 +4370,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4784,9 +4388,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4804,9 +4406,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>1260
-```
-```</t>
+          <t>1260</t>
         </is>
       </c>
     </row>
@@ -4824,9 +4424,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4844,9 +4442,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4864,8 +4460,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4883,9 +4478,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4903,9 +4496,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4923,9 +4514,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4961,9 +4550,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -4981,9 +4568,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5001,9 +4586,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5021,9 +4604,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5041,9 +4622,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5061,9 +4640,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5081,9 +4658,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5101,9 +4676,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5121,9 +4694,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5141,9 +4712,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5161,9 +4730,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5181,8 +4748,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Not applicable
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -5200,9 +4766,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5220,9 +4784,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5240,9 +4802,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5278,9 +4838,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>PR
-```
-```</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -5298,9 +4856,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5318,9 +4874,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5338,9 +4892,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -5358,9 +4910,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5378,9 +4928,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -5398,9 +4946,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5418,9 +4964,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5438,9 +4982,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>24
-```
-```</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -5458,9 +5000,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,9 +5018,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5498,8 +5036,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5517,9 +5054,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5537,9 +5072,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5557,9 +5090,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5595,9 +5126,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -5615,9 +5144,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5635,9 +5162,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>1997-2019
-```
-```</t>
+          <t>1997-2019</t>
         </is>
       </c>
     </row>
@@ -5655,9 +5180,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -5675,9 +5198,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5695,9 +5216,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Whole blood
-```
-```</t>
+          <t>Whole blood</t>
         </is>
       </c>
     </row>
@@ -5715,9 +5234,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5735,9 +5252,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5755,9 +5270,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>223
-```
-```</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -5775,9 +5288,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5795,9 +5306,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>INSTI, NRTI
-```
-```</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
     </row>
@@ -5815,8 +5324,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Bictegravir, Emtricitabine, Tenofovir alafenamide
-```</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir alafenamide</t>
         </is>
       </c>
     </row>
@@ -5834,9 +5342,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5854,9 +5360,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5874,9 +5378,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5912,9 +5414,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Env, NC
-```
-```</t>
+          <t>Env, NC</t>
         </is>
       </c>
     </row>
@@ -5932,9 +5432,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>United Kingdom
-```
-```</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -5952,9 +5450,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2015–2021
-```
-```</t>
+          <t>2015–2021</t>
         </is>
       </c>
     </row>
@@ -5972,9 +5468,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -5992,9 +5486,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6012,9 +5504,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -6032,9 +5522,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6052,9 +5540,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6072,9 +5558,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1182
-```
-```</t>
+          <t>1182</t>
         </is>
       </c>
     </row>
@@ -6092,9 +5576,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6112,9 +5594,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6132,8 +5612,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6151,9 +5630,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6171,9 +5648,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6191,9 +5666,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6229,9 +5702,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6249,9 +5720,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6269,9 +5738,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6289,9 +5756,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6309,9 +5774,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6329,9 +5792,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6349,9 +5810,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6369,9 +5828,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6389,9 +5846,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>249
-```
-```</t>
+          <t>249</t>
         </is>
       </c>
     </row>
@@ -6409,9 +5864,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6429,9 +5882,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6449,8 +5900,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6468,9 +5918,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6488,9 +5936,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6508,9 +5954,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6546,9 +5990,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -6566,9 +6008,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Mozambique
-```
-```</t>
+          <t>Mozambique</t>
         </is>
       </c>
     </row>
@@ -6586,9 +6026,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2023–2024
-```
-```</t>
+          <t>2023–2024</t>
         </is>
       </c>
     </row>
@@ -6606,9 +6044,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -6626,9 +6062,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6646,9 +6080,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -6666,9 +6098,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6686,9 +6116,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6706,9 +6134,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>28
-```
-```</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -6726,9 +6152,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6746,9 +6170,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6766,8 +6188,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6785,9 +6206,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6805,9 +6224,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6825,9 +6242,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6863,9 +6278,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -6883,9 +6296,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Cameroon
-```
-```</t>
+          <t>Cameroon</t>
         </is>
       </c>
     </row>
@@ -6903,9 +6314,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2022-2023
-```
-```</t>
+          <t>2022-2023</t>
         </is>
       </c>
     </row>
@@ -6923,9 +6332,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -6943,9 +6350,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6963,9 +6368,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -6983,9 +6386,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7003,9 +6404,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7023,9 +6422,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>203
-```
-```</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -7043,9 +6440,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7063,9 +6458,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -7083,8 +6476,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>ABC, 3TC, EFV, NVP, AZT, DTG, ATV, LPV, TDF
-```</t>
+          <t>ABC, 3TC, EFV, NVP, AZT, DTG, ATV, LPV, TDF</t>
         </is>
       </c>
     </row>
@@ -7102,9 +6494,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7122,9 +6512,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7142,9 +6530,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7180,9 +6566,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>CA
-```
-```</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -7200,9 +6584,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic
-```
-```</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
     </row>
@@ -7220,9 +6602,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2019–2020
-```
-```</t>
+          <t>2019–2020</t>
         </is>
       </c>
     </row>
@@ -7240,9 +6620,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7260,9 +6638,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7280,9 +6656,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -7300,9 +6674,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7320,9 +6692,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7340,9 +6710,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>182
-```
-```</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -7360,9 +6728,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7380,9 +6746,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
     </row>
@@ -7400,8 +6764,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Emtricitabine (FTC); Tenofovir alafenamide (TAF); Bictegravir (BIC); Lenacapavir (LEN)
-```</t>
+          <t>Emtricitabine (FTC); Tenofovir alafenamide (TAF); Bictegravir (BIC); Lenacapavir (LEN)</t>
         </is>
       </c>
     </row>
@@ -7419,9 +6782,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7439,9 +6800,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7459,9 +6818,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7497,9 +6854,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol, CA, Env
-```
-```</t>
+          <t>PR, RT, IN, Pol, CA, Env</t>
         </is>
       </c>
     </row>
@@ -7517,9 +6872,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Uganda
-```
-```</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -7537,9 +6890,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2018–2023
-```
-```</t>
+          <t>2018–2023</t>
         </is>
       </c>
     </row>
@@ -7557,9 +6908,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7577,9 +6926,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7597,9 +6944,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7617,9 +6962,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7637,9 +6980,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7657,9 +6998,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>235
-```
-```</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -7677,9 +7016,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7697,9 +7034,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -7717,8 +7052,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>ABC, AZT, TDF, FTC, LPV, RTV, d4T, DRV, RAL
-```</t>
+          <t>ABC, AZT, TDF, FTC, LPV, RTV, d4T, DRV, RAL</t>
         </is>
       </c>
     </row>
@@ -7736,9 +7070,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7756,9 +7088,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7776,9 +7106,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7814,9 +7142,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Pol
-```
-```</t>
+          <t>Pol</t>
         </is>
       </c>
     </row>
@@ -7834,9 +7160,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>China
-```
-```</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -7854,9 +7178,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2023
-```
-```</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7874,9 +7196,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -7894,9 +7214,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7914,9 +7232,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Plasma, whole blood
-```
-```</t>
+          <t>Plasma, whole blood</t>
         </is>
       </c>
     </row>
@@ -7934,9 +7250,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7954,9 +7268,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7974,9 +7286,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>1
-```
-```</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7994,9 +7304,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8014,9 +7322,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8034,8 +7340,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8053,9 +7358,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8073,9 +7376,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8093,9 +7394,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8131,9 +7430,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>PR
-```
-```</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -8151,9 +7448,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8171,9 +7466,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8191,9 +7484,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8211,9 +7502,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8231,9 +7520,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8251,9 +7538,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8271,9 +7556,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8291,9 +7574,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8311,9 +7592,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8331,9 +7610,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8351,8 +7628,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8370,9 +7646,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8390,9 +7664,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8410,9 +7682,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8448,9 +7718,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Pol
-```
-```</t>
+          <t>Pol</t>
         </is>
       </c>
     </row>
@@ -8468,9 +7736,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>China, United States
-```
-```</t>
+          <t>China, United States</t>
         </is>
       </c>
     </row>
@@ -8488,9 +7754,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>1978–2023
-```
-```</t>
+          <t>1978–2023</t>
         </is>
       </c>
     </row>
@@ -8508,9 +7772,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -8528,9 +7790,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8548,9 +7808,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -8568,9 +7826,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -8588,9 +7844,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8608,9 +7862,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8628,9 +7880,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -8648,9 +7898,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -8668,8 +7916,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Not applicable
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -8687,9 +7934,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8707,9 +7952,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8727,9 +7970,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8765,9 +8006,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>RT
-```
-```</t>
+          <t>RT</t>
         </is>
       </c>
     </row>
@@ -8785,9 +8024,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Senegal
-```
-```</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
@@ -8805,9 +8042,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2017-2018
-```
-```</t>
+          <t>2017-2018</t>
         </is>
       </c>
     </row>
@@ -8825,9 +8060,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -8845,9 +8078,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8865,9 +8096,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Plasma, DBS
-```
-```</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
     </row>
@@ -8885,9 +8114,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8905,9 +8132,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8925,9 +8150,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>237
-```
-```</t>
+          <t>237</t>
         </is>
       </c>
     </row>
@@ -8945,9 +8168,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8965,9 +8186,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8985,8 +8204,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9004,9 +8222,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9024,9 +8240,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9044,9 +8258,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9082,9 +8294,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -9102,9 +8312,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Uganda
-```
-```</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -9122,9 +8330,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2021
-```
-```</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -9142,9 +8348,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -9162,9 +8366,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9182,9 +8384,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -9202,9 +8402,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9222,9 +8420,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9242,9 +8438,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>333
-```
-```</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -9262,9 +8456,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9282,9 +8474,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -9302,8 +8492,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>DTG, LPV/r, EFV, NVP, ABC, AZT, TDF, 3TC
-```</t>
+          <t>DTG, LPV/r, EFV, NVP, ABC, AZT, TDF, 3TC</t>
         </is>
       </c>
     </row>
@@ -9321,9 +8510,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9341,9 +8528,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9361,9 +8546,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9399,9 +8582,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>CA, PR, RT, IN
-```
-```</t>
+          <t>CA, PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -9419,9 +8600,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9439,9 +8618,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9459,9 +8636,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -9479,9 +8654,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9499,9 +8672,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -9519,9 +8690,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9539,9 +8708,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9559,9 +8726,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>52
-```
-```</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -9579,9 +8744,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9599,9 +8762,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>NRTI
-```
-```</t>
+          <t>NRTI</t>
         </is>
       </c>
     </row>
@@ -9619,8 +8780,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9638,9 +8798,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9658,9 +8816,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9678,9 +8834,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9716,9 +8870,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -9736,9 +8888,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Kenya, Uganda, Tanzania, Ethiopia
-```
-```</t>
+          <t>Kenya, Uganda, Tanzania, Ethiopia</t>
         </is>
       </c>
     </row>
@@ -9756,9 +8906,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9776,9 +8924,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9796,9 +8942,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9816,9 +8960,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9836,9 +8978,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9856,9 +8996,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9876,9 +9014,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9896,9 +9032,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9916,9 +9050,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9936,8 +9068,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9955,9 +9086,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
